--- a/reports/model_comparison.xlsx
+++ b/reports/model_comparison.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -480,7 +480,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-10 23:51:37</t>
+          <t>2026-02-24 21:24:58</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -585,14 +585,14 @@
         <v>192</v>
       </c>
       <c r="C10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -606,14 +606,14 @@
         <v>192</v>
       </c>
       <c r="C11" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -635,6 +635,27 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>72.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>192</v>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>172</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10.4%</t>
         </is>
       </c>
     </row>
@@ -652,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -797,86 +818,86 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>formatting_tricks</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>distilgpt2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gpt-oss-20b-exj</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -887,17 +908,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>gpt-oss-20b-exj</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -908,285 +929,285 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>gpt2</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>12</v>
       </c>
       <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
         <v>9</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>hijacking</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>distilgpt2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>25</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>21</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>gpt-oss-20b-exj</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>18</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>18</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>25</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>gpt-oss-20b-exj</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>gpt2</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>24.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>72.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>25</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>22</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>indirect_injection</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>distilgpt2</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>gpt2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1204,705 +1225,734 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gpt2</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>instruction_override</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Pass Rate</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>distilgpt2</t>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>gpt-oss-20b-exj</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>21</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>21</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>gpt2</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>34</v>
-      </c>
-      <c r="C38" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" t="n">
-        <v>30</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>11.8%</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>instruction_override</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>34</v>
-      </c>
-      <c r="C39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" t="n">
-        <v>25</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>26.5%</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>34</v>
       </c>
       <c r="C40" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>11.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gpt-oss-20b-exj</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>21</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>21</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>jailbreak</t>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>gpt2</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>34</v>
+      </c>
+      <c r="C42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" t="n">
+        <v>30</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Pass Rate</t>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>34</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>26</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23.5%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>distilgpt2</t>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>34</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>33</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>jailbreak</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>distilgpt2</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>24</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>gpt-oss-20b-exj</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B50" t="n">
         <v>28</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C50" t="n">
         <v>0</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D50" t="n">
         <v>28</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>gpt2</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B51" t="n">
         <v>30</v>
       </c>
-      <c r="C46" t="n">
-        <v>8</v>
-      </c>
-      <c r="D46" t="n">
-        <v>22</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>30</v>
-      </c>
-      <c r="C47" t="n">
-        <v>22</v>
-      </c>
-      <c r="D47" t="n">
-        <v>8</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>73.3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>30</v>
-      </c>
-      <c r="C48" t="n">
-        <v>29</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>multilingual</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>Pass Rate</t>
+      <c r="C51" t="n">
+        <v>10</v>
+      </c>
+      <c r="D51" t="n">
+        <v>20</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>distilgpt2</t>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D52" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>gpt-oss-20b-exj</t>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>96.7%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>30</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="n">
+        <v>26</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>multilingual</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>distilgpt2</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
         <v>25</v>
       </c>
-      <c r="C54" t="n">
-        <v>2</v>
-      </c>
-      <c r="D54" t="n">
-        <v>23</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>8.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>25</v>
-      </c>
-      <c r="C55" t="n">
-        <v>10</v>
-      </c>
-      <c r="D55" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>25</v>
-      </c>
-      <c r="C56" t="n">
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="n">
         <v>22</v>
       </c>
-      <c r="D56" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>88.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>psychological_manipulation</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>12.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>Pass Rate</t>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gpt-oss-20b-exj</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>20</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>20</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>distilgpt2</t>
+          <t>gpt2</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>25</v>
       </c>
       <c r="C60" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gpt-oss-20b-exj</t>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D61" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>25</v>
       </c>
       <c r="C62" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D62" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>88.0%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>25</v>
       </c>
       <c r="C63" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D63" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>76.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
+          <t>8.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>psychological_manipulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>distilgpt2</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
         <v>25</v>
       </c>
-      <c r="C64" t="n">
-        <v>21</v>
-      </c>
-      <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>84.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>role_playing</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>Pass Rate</t>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>18</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>28.0%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>distilgpt2</t>
+          <t>gpt-oss-20b-exj</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>gpt-oss-20b-exj</t>
+          <t>gpt2</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>32.0%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D70" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C71" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>secret_extraction</t>
+          <t>role_playing</t>
         </is>
       </c>
     </row>
@@ -1940,17 +1990,17 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>
@@ -1982,17 +2032,17 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -2003,17 +2053,17 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" t="n">
         <v>6</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -2024,32 +2074,213 @@
         </is>
       </c>
       <c r="B80" t="n">
+        <v>13</v>
+      </c>
+      <c r="C80" t="n">
+        <v>10</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>13</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>secret_extraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>distilgpt2</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
         <v>15</v>
       </c>
-      <c r="C80" t="n">
-        <v>6</v>
-      </c>
-      <c r="D80" t="n">
-        <v>9</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>40.0%</t>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>14</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>6.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>gpt-oss-20b-exj</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>11</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>11</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>gpt2</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>15</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>12</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>15</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>15</v>
+      </c>
+      <c r="C89" t="n">
+        <v>7</v>
+      </c>
+      <c r="D89" t="n">
+        <v>8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>15</v>
+      </c>
+      <c r="C90" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" t="n">
+        <v>12</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A47:E47"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A66:E66"/>
-    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2062,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2165,14 +2396,14 @@
         <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -2186,14 +2417,14 @@
         <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>75.3%</t>
         </is>
       </c>
     </row>
@@ -2207,440 +2438,524 @@
         <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>88.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+          <t>87.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>81</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>71</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>distilgpt2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>67</v>
-      </c>
-      <c r="C13" t="n">
-        <v>6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>9.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gpt-oss-20b-exj</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>gpt-oss-20b-exj</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>gpt2</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>67</v>
       </c>
       <c r="C16" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>67</v>
       </c>
       <c r="C17" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>41.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>67</v>
+      </c>
+      <c r="C18" t="n">
+        <v>49</v>
+      </c>
+      <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>73.1%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>67</v>
+      </c>
+      <c r="C19" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>10.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>distilgpt2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>37</v>
-      </c>
-      <c r="C21" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" t="n">
-        <v>34</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>8.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>gpt-oss-20b-exj</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>23</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>23</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gpt2</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>37</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>gpt-oss-20b-exj</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+          <t>gpt2</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>37</v>
       </c>
       <c r="C25" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>37</v>
+      </c>
+      <c r="C26" t="n">
+        <v>8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>29</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>21.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>37</v>
+      </c>
+      <c r="C27" t="n">
         <v>17</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D27" t="n">
         <v>20</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>45.9%</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>37</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Pass Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>distilgpt2</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>7</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="n">
-        <v>5</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>gpt-oss-20b-exj</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>gpt2</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>7</v>
-      </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="n">
-        <v>5</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>28.6%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+          <t>distilgpt2</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>7</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>gpt-oss-20b-exj</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>gpt2</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>meta-llama/Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>meta-llama/Meta-Llama-3-70B-Instruct</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B36" t="n">
         <v>7</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C36" t="n">
         <v>3</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D36" t="n">
         <v>4</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>42.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TinyLlama/TinyLlama-1.1B-Chat-v1.0</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>7</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
